--- a/output/pdf_financials_xlsx/PTX.xlsx
+++ b/output/pdf_financials_xlsx/PTX.xlsx
@@ -1932,13 +1932,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>2.346694</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>2.824419</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>2.990719</v>
       </c>
     </row>
     <row r="93">
@@ -3168,7 +3168,11 @@
           <t>Share-based payment reserve (note 12)</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>-</t>
@@ -3579,7 +3583,11 @@
           <t>Share-based payment reserve (note 13)</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E30" s="5" t="n">
         <v>2.346694</v>
       </c>

--- a/output/pdf_financials_xlsx/PTX.xlsx
+++ b/output/pdf_financials_xlsx/PTX.xlsx
@@ -982,13 +982,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>2.54508</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>2.739016</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>1.723067</v>
       </c>
     </row>
     <row r="35">
@@ -1014,13 +1014,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>2.54508</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>2.739016</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>1.723067</v>
       </c>
     </row>
     <row r="37">
@@ -1206,13 +1206,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>2.629637</v>
+        <v>0.08455699999999999</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>3.2113</v>
+        <v>0.472284</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>2.337361</v>
+        <v>0.614294</v>
       </c>
     </row>
     <row r="49">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">

--- a/output/pdf_financials_xlsx/PTX.xlsx
+++ b/output/pdf_financials_xlsx/PTX.xlsx
@@ -529,13 +529,13 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.573604</v>
+        <v>0.750358</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.747856</v>
+        <v>1.036331</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>1.773144</v>
+        <v>2.066704</v>
       </c>
     </row>
     <row r="8">
@@ -577,13 +577,13 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.573604</v>
+        <v>0.750358</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.747856</v>
+        <v>1.036331</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>1.773144</v>
+        <v>2.066704</v>
       </c>
     </row>
     <row r="11">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>-0.573604</v>
+        <v>-0.750358</v>
       </c>
       <c r="C11" s="3" t="n">
         <v>-2.908528</v>
@@ -4964,7 +4964,11 @@
           <t>Management and directors' fees (note 15)</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr"/>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E75" t="inlineStr">
         <is>
           <t>-</t>
@@ -5630,7 +5634,11 @@
           <t>Management and directors' fees (note 16)</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr"/>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E97" s="5" t="n">
         <v>0.176754</v>
       </c>
